--- a/LRB_VikramProcter_BOM_Full.xlsx
+++ b/LRB_VikramProcter_BOM_Full.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikra\Documents\School\SOAR\LaunchRailBoard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3608DB5A-A736-477B-8F46-A5FD6287ECA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6FE8AB-FB9A-4B0D-8D6F-8D719EA67667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8FCAF11A-7D9D-431D-91CB-390786A526BC}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" xr2:uid="{8FCAF11A-7D9D-431D-91CB-390786A526BC}"/>
   </bookViews>
   <sheets>
     <sheet name="LRB_VikramProcter_BOM_Full" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="327">
   <si>
     <t>Line #</t>
   </si>
@@ -1011,6 +1011,15 @@
   </si>
   <si>
     <t>535-9830-1-ND</t>
+  </si>
+  <si>
+    <t>RCWCTE</t>
+  </si>
+  <si>
+    <t>Microchip Technology</t>
+  </si>
+  <si>
+    <t>Stackpole Electronics Inc</t>
   </si>
 </sst>
 </file>
@@ -2199,7 +2208,9 @@
         <v>14</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>324</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -2417,7 +2428,9 @@
         <v>1</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>430450800</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -3348,8 +3361,12 @@
       <c r="G50" s="1">
         <v>6</v>
       </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="H50" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -3534,8 +3551,12 @@
       <c r="G55" s="1">
         <v>2</v>
       </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
